--- a/data.xlsx
+++ b/data.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -449,7 +449,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
@@ -618,27 +618,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06/02/2026 10:19</t>
+          <t>10/02/2026 12:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mD2334</t>
+          <t>MK08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>andrianasoavina victorien</t>
+          <t>Rafanomezantsoa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+261325504441</t>
+          <t>+261324404442</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>andrianasoavinaVictorien@gmail.com</t>
+          <t>test@dadavic.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -668,39 +668,94 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sur mesure</t>
+          <t>À la carte</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Circuit aventure</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Individuel</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Eugene</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3 jours</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>+261324404442</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10/02/2026 12:47</t>
+          <t>09/02/2026 19:09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MK08</t>
+          <t>CLAM1212</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rafanomezantsoa</t>
+          <t>manambimana</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+261324404442</t>
+          <t>+261343677234</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>test@dadavic.com</t>
+          <t>andriavict@gmail.com</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -715,114 +770,64 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hôtel 2*</t>
+          <t>Hôtel 4*</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Triple</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2 à 6 ans</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>À la carte</t>
+          <t>Sur mesure</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Circuit aventure</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Individuel</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Eugene</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>24/02/2026</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>27/02/2026</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>3 jours</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>+261324404442</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/02/2026 19:09</t>
+          <t>16/02/2026 20:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CLAM1212</t>
+          <t>FG004</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>manambimana</t>
+          <t>innocente</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+261343677234</t>
+          <t>+261322208765</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>andriavict@gmail.com</t>
+          <t>tsiky@gmail.com</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Moyenne saison</t>
+          <t>Basse saison</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -837,54 +842,104 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Triple</t>
+          <t>Double/twin</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2 à 6 ans</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sur mesure</t>
+          <t>À la carte</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Circuit aventure</t>
+          <t>Circuits aventure</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Tsiky</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3 jours</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>+261322208765</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16/02/2026 20:38</t>
+          <t>17/02/2026 10:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FG004</t>
+          <t>GH56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>innocente</t>
+          <t>dollard</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+261322208765</t>
+          <t>+261334555667</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tsiky@gmail.com</t>
+          <t>test@Hotmail.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -919,7 +974,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Circuits aventure</t>
+          <t>Circuit Tourisme Solidaire</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -929,89 +984,89 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Tsiky</t>
+          <t>rabe</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>18/02/2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>3 jours</t>
+          <t>2 jours</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>+261334555667</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>+261322208765</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17/02/2026 10:31</t>
+          <t>23/02/2026 16:10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GH56</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dollard</t>
+          <t>okok</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+261334555667</t>
+          <t>+261343455508</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>test@Hotmail.com</t>
+          <t>test4@test.com</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Basse saison</t>
+          <t>Moyenne saison</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Demi-pension</t>
+          <t>All inclusive</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1036,60 +1091,187 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Circuit Tourisme Solidaire</t>
+          <t>Circuits aventure</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>Individuel</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>test34</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>8 jours</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>+261343455508</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>23/02/2026 17:13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mandimby</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+261325509877</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rakoto.mandimby@coucou.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hôtel 3*</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Double/twin</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>À la carte</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Le boucle en pays Betsileo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Groupe</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>rabe</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>18/02/2026</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>20/02/2026</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2 jours</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>rakoto</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>14 jours</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>+261334555667</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>+261325509877</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1106,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1659,7 +1841,6 @@
           <t>2026-02-18 14:14:46</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>FG004</t>
@@ -1703,6 +1884,169 @@
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-23 16:11:40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GRAN URBAN HOTEL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>All inclusive</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-23 16:20:29</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>okok test34</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GRAN URBAN HOTEL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>All inclusive</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>690000</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-23 19:39:29</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mandimby rakoto</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GRAN URBAN HOTEL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>14</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>8131900</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Ariary</t>
         </is>
@@ -1719,7 +2063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1888,6 +2232,36 @@
           <t>FML</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ID Circuit</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Itinéraire Circuit</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Activité Circuit</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Durée Circuit</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Condition Physique Circuit</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Type Voiture Circuit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2170,6 +2544,330 @@
       <c r="AE3" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>23/02/2026 16:10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Individuel</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>test34</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>okok</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8 jours</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>+261343455508</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>+261343455508</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>test4@test.com</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>All inclusive</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Hôtel 4*</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Double/twin</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>À la carte</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Circuits aventure</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Circuits aventure</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Antsirabe, Ambositra, FIANARANTSOA</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3*</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>23/02/2026 17:13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>rakoto</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>mandimby</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>14 jours</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>+261325509877</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>+261325509877</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rakoto.mandimby@coucou.com</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Hôtel 3*</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Double/twin</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>À la carte</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Le boucle en pays Betsileo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Le boucle en pays Betsileo</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Ambositra, Ambohimitombo, Itazonana, Ifaliarivo, Sakaivo, Antoetra, Ambatofinandrahana, Ihazofotsy, Itremo, antsirabe, Antananarivo</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3*</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Antananarivo, Ambositra, Ambohimitombo, Itazonana, Ifaliarivo, Sakaivo, Antoetra, Ambatofinandrahana, Ihazofotsy, Itremo, Ambositra, antsirabe, Antananarivo</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Campement a cote de l'une des plus hautes cascades de Madagascar, Visite de l'artisans et de marches artisanaux , Rencontre  et echange avec la population locale, Les Zafimaniry, les experts de la sculpture sur bois, Randonnee  dans la brousse malagasy, La decouverte d'un site peu connu avec faune et flore exceptionnelles</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>12 jours</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Tres bon marcheur</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>4*4 tout terrain</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1288,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2003,7 +2003,6 @@
           <t>2026-02-23 19:39:29</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>mandimby rakoto</t>
@@ -2047,6 +2046,61 @@
         <v>8131900</v>
       </c>
       <c r="M13" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:45:23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mandimby rakoto</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GRAN URBAN HOTEL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>8131900</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>Ariary</t>
         </is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -440,12 +440,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB7"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -457,7 +457,7 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
@@ -1277,6 +1277,138 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>24/02/2026 15:51</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fluide</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+261345567668</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>akory@koto.mg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hôtel 4*</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Double/twin</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>À la carte</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Sur la route du sud de Madagascar</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>kokokoto</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>28 jours</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>+261345567668</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1288,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2057,7 +2189,6 @@
           <t>2026-02-24 09:45:23</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>mandimby rakoto</t>
@@ -2101,6 +2232,242 @@
         <v>8131900</v>
       </c>
       <c r="M14" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>fluide kokokoto</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GRAN URBAN HOTEL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>28</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>16345700</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>fluide kokokoto</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CHAMBRE DES VOYAGEURS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Antsirabe</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>6160000</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fluide kokokoto</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CENTREST</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RANOMAFANA</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fluide kokokoto</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CHEZ CECILE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IFATY</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>28</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2660000</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>Ariary</t>
         </is>
@@ -2117,7 +2484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM5"/>
+  <dimension ref="A1:AM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2922,6 +3289,188 @@
       <c r="AM5" t="inlineStr">
         <is>
           <t>4*4 tout terrain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>24/02/2026 15:51</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DS3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Groupe</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>kokokoto</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>fluide</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>28 jours</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>+261345567668</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>+261345567668</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>akory@koto.mg</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Hôtel 4*</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Double/twin</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>À la carte</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Sur la route du sud de Madagascar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Sur la route du sud de Madagascar</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>antsirabe, Zafimaniry, Ranomafana, Ambalavao, Andingitra, Ranohira (Isalo), Tuler, Ifaty, Antananarivo</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Antananarivo, antsirabe, Zafimaniry, Ranomafana, Ambalavao, Andingitra, Ranohira (Isalo), Tuler, Ifaty, Antananarivo</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Rencontre et partage, Rencontre avec les artisans d'Ambatolampy, Randonnee VIT a antsirabe, Trekking chez les Zafimaniry, Visite des pars nationaux de Madagascar, Ballade a la vallee de Tsaranoro, Faunes et flores endemiques, Rencontre et echange avec la population locale, LA plage et le soleil du canal de Mozambique</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>15 jours</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Bon marcheur</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Tout terrain/minibus /berline</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,24 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEMANDE_CLIENT" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COTATION_H" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INFOS_CLIENTS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COTATION_FRAIS_COL" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,11 +28,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -44,14 +43,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0027AE60"/>
-        <bgColor rgb="0027AE60"/>
+        <fgColor rgb="FF27AE60"/>
+        <bgColor rgb="FF27AE60"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +76,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -440,24 +439,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="11" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
@@ -466,11 +463,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="6" customWidth="1" min="24" max="24"/>
-    <col width="6" customWidth="1" min="25" max="25"/>
-    <col width="6" customWidth="1" min="26" max="26"/>
-    <col width="6" customWidth="1" min="27" max="27"/>
-    <col width="6" customWidth="1" min="28" max="28"/>
+    <col width="6" customWidth="1" min="24" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1274,6 +1267,123 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>24/02/2026 11:12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RF345</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RABE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+2610329843459</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>fenosoa@yeiayelconsulting.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Demi-pension</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hôtel 3*</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Familliale</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>À la carte</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Montrez-moi le fleuve Manambolo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Individuel</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Fenosoa</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>32 jours</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>+2610329843459</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1288,8 +1398,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1298,8 +1408,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="8" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -2003,7 +2112,6 @@
           <t>2026-02-23 19:39:29</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>mandimby rakoto</t>
@@ -2047,6 +2155,60 @@
         <v>8131900</v>
       </c>
       <c r="M13" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:45:23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mandimby rakoto</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GRAN URBAN HOTEL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>8131900</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>Ariary</t>
         </is>
@@ -2063,8 +2225,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AM6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -2868,10 +3030,380 @@
       <c r="AM5" t="inlineStr">
         <is>
           <t>4*4 tout terrain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>24/02/2026 11:12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RF345</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Individuel</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fenosoa</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RABE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>32 jours</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>+2610329843459</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>+2610329843459</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>fenosoa@yeiayelconsulting.com</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Demi-pension</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Hôtel 3*</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Familliale</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>À la carte</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Montrez-moi le fleuve Manambolo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Montrez-moi le fleuve Manambolo</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>ampefy, Tsiroanomandidy, Massif Bongolava, Manambolo, Bekopaka, Morondava, Antananarivo</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Antananarivo, ampefy, Tsiroanomandidy, Massif Bongolava, Manambolo, Bekopaka, Morondava, Antananarivo</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Rendonnees et descente du fleuve</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>13 jours/ 12 nuits</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Bon marcheur</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Tout terrain</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ID_Client</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Nom_Client</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Forfait</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Prestataire</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Désignation</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>MONTANT</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>QUANTITE</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:13:03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RF345</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RAKOTO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Forfait 1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Guide du Tsingy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:54:58</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mandimby</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Travels d'Anosy</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guide full fort dauphin</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2000000.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-24 14:54:58</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mandimby</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Forfait 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Travels guide Mada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Guide full options</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3000000.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1420,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2473,6 +2473,124 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:12:26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>fluide kokokoto</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>COMBAVA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>28</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>7280000</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:12:27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>fluide kokokoto</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PLUMERIA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Antsirabe</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>28</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>5908000</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEMANDE_CLIENT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COTATION_H" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INFOS_CLIENTS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DEMANDE_CLIENT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="COTATION_H" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="INFOS_CLIENTS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Journal" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB8"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -449,7 +450,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
@@ -457,7 +458,7 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
@@ -1409,6 +1410,123 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>26/02/2026 09:11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mimitry</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+261334544567</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>dimitryVict@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sans restauration</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Hôtel 4*</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Double/twin</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>À la carte</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Montrez-moi le fleuve Manambolo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Individuel</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>VICCCTTRTRTY</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>43 jours</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>+261334544567</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1420,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2591,6 +2709,419 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-24 23:16:52</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>fluide kokokoto</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CHEZ CECILE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>IFATY</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>28</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>2660000</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-24 23:16:52</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>fluide kokokoto</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CHAMBRE DES VOYAGEURS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Antsirabe</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>28</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Pension complète</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>6160000</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:14:34</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mimitry VICCCTTRTRTY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BElVEDERE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sans restauration</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:14:34</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>mimitry VICCCTTRTRTY</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SOLEIL DES TSINGY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BEKOPAKA</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Standard / Double</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sans restauration</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:14:34</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mimitry VICCCTTRTRTY</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HOTEL DE MENABE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MORONDAVA</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>De luxe / Double</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sans restauration</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>456000</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:22:51</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mimitry VICCCTTRTRTY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LA VILLETTE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Suite / Single</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sans restauration</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>643.1999999999999</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:22:51</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mimitry VICCCTTRTRTY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SOLEIL DES TSINGY</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BEKOPAKA</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bungalows / Twin</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sans restauration</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2602,7 +3133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM6"/>
+  <dimension ref="A1:AM7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3592,6 +4123,875 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>26/02/2026 09:11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GT67</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Individuel</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>VICCCTTRTRTY</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>mimitry</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>43 jours</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>+261334544567</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>+261334544567</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>dimitryVict@gmail.com</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Moyenne saison</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Sans restauration</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Hôtel 4*</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Double/twin</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>À la carte</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Montrez-moi le fleuve Manambolo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Montrez-moi le fleuve Manambolo</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Antananarivo</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>ampefy, Tsiroanomandidy, Massif Bongolava, Manambolo, Bekopaka, Morondava, Antananarivo</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Antananarivo, ampefy, Tsiroanomandidy, Massif Bongolava, Manambolo, Bekopaka, Morondava, Antananarivo</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Rendonnees et descente du fleuve</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>13 jours/ 12 nuits</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Bon marcheur</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Tout terrain</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DateValeur</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MontantDébit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>MontantCrédit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CompteDébit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>CompteCrédit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Année</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-06 12:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[LHM:H:5] Client Démo / Hôtel Démo / Fianarantsoa (Ariary)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-02-06 12:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>99999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>99999</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-23 16:20:29</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[LHM:H:12] okok test34 / GRAN URBAN HOTEL / Antananarivo (Ariary)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-02-23 16:20:29</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>690000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>690000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-23 19:39:29</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[LHM:H:13] mandimby rakoto / GRAN URBAN HOTEL / Antananarivo (Ariary)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-02-23 19:39:29</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8131900</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8131900</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:45:23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[LHM:H:14] mandimby rakoto / GRAN URBAN HOTEL / Antananarivo (Ariary)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-02-24 09:45:23</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8131900</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8131900</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[LHM:H:15] fluide kokokoto / GRAN URBAN HOTEL / Antananarivo (Ariary)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16345700</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16345700</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[LHM:H:16] fluide kokokoto / CHAMBRE DES VOYAGEURS / Antsirabe (Ariary)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6160000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6160000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[LHM:H:17] fluide kokokoto / CENTREST / RANOMAFANA (Ariary)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[LHM:H:18] fluide kokokoto / CHEZ CECILE / IFATY (Ariary)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-02-24 16:06:46</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2660000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2660000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:12:26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[LHM:H:19] fluide kokokoto / COMBAVA / Antananarivo (Ariary)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:12:26</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7280000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7280000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:12:27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[LHM:H:20] fluide kokokoto / PLUMERIA / Antsirabe (Ariary)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-02-24 17:12:27</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5908000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5908000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-24 23:16:52</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[LHM:H:21] fluide kokokoto / CHEZ CECILE / IFATY (Ariary)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-02-24 23:16:52</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2660000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2660000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-24 23:16:52</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[LHM:H:22] fluide kokokoto / CHAMBRE DES VOYAGEURS / Antsirabe (Ariary)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-02-24 23:16:52</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6160000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6160000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:14:34</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[LHM:H:23] mimitry VICCCTTRTRTY / BElVEDERE / Antananarivo (Ariary)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:14:34</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:14:34</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[LHM:H:24] mimitry VICCCTTRTRTY / SOLEIL DES TSINGY / BEKOPAKA (Ariary)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:14:34</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>316.8</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:14:34</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[LHM:H:25] mimitry VICCCTTRTRTY / HOTEL DE MENABE / MORONDAVA (Ariary)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:14:34</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>456000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>456000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:22:51</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[LHM:H:26] mimitry VICCCTTRTRTY / LA VILLETTE / Antananarivo (Ariary)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:22:51</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>643.1999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>643.1999999999999</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:22:51</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[LHM:H:27] mimitry VICCCTTRTRTY / SOLEIL DES TSINGY / BEKOPAKA (Ariary)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:22:51</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>411000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>706000</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -11,6 +11,8 @@
     <sheet name="COTATION_H" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="INFOS_CLIENTS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Journal" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FACTURES_CLIENTS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ETAT_FINANCIER_AUTO" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +38,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +57,12 @@
         <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,12 +76,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4995,4 +5006,370 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ID_Facture</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Source_Type</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Source_Ref</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Client_ID</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Client_Nom</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Devise</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Montant_HT</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Cout_HT</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Marge_%</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Marge_Montant</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Base_Taxable_HT</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>TVA_%</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>TVA_Montant</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Total_TTC</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Acompte</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Reste_A_Payer</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-27 10:50:59</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FAC-202602-0001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Devis client</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DEVIS_CLIENT:3435</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>mimitry VICCCTTRTRTY</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>457696.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" t="n">
+        <v>54923.61599999999</v>
+      </c>
+      <c r="L2" t="n">
+        <v>512620.416</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N2" t="n">
+        <v>102524.0832</v>
+      </c>
+      <c r="O2" t="n">
+        <v>615144.4992</v>
+      </c>
+      <c r="P2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>415144.4992</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>payée avec acompte</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-27 10:53:04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FAC-202602-0002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Hôtel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Hôtel#21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ED3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fluide kokokoto</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ariary</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2660000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K3" t="n">
+        <v>319200</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2979200</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N3" t="n">
+        <v>595840</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3575040</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3575040</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>payée</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Date_MAJ</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Nb_Factures</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>CA_HT</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Marge_Totale</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TVA_Totale</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>CA_TTC</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Acomptes_Recus</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Encaissements_Estimes</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Restes_A_Encaisser</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Nb_Payees</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Nb_Payees_Avec_Acompte</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Nb_Non_Payees</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-27 10:53:06</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3117696.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>374123.616</v>
+      </c>
+      <c r="E2" t="n">
+        <v>698364.0832</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4190184.4992</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3775040</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3775040</v>
+      </c>
+      <c r="I2" t="n">
+        <v>415144.4992</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -5170,14 +5170,14 @@
         <v>615144.4992</v>
       </c>
       <c r="P2" t="n">
-        <v>200000</v>
+        <v>615144.4992</v>
       </c>
       <c r="Q2" t="n">
-        <v>415144.4992</v>
+        <v>0</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>payée avec acompte</t>
+          <t>payée</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-27 10:53:06</t>
+          <t>2026-02-27 13:17:37</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5351,19 +5351,19 @@
         <v>4190184.4992</v>
       </c>
       <c r="G2" t="n">
-        <v>3775040</v>
+        <v>4190184.4992</v>
       </c>
       <c r="H2" t="n">
-        <v>3775040</v>
+        <v>4190184.4992</v>
       </c>
       <c r="I2" t="n">
-        <v>415144.4992</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
